--- a/exports/trend_1d/MCX_full_report.xlsx
+++ b/exports/trend_1d/MCX_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>10.48</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42117</v>
+        <v>42118</v>
       </c>
       <c r="H2" t="n">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="I2" t="n">
         <v>210.4095438039395</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K2" t="n">
-        <v>25.88</v>
+        <v>20.59</v>
       </c>
       <c r="L2" t="n">
         <v>1.76</v>
@@ -555,7 +578,7 @@
         <v>1.28</v>
       </c>
       <c r="N2" t="n">
-        <v>3.85</v>
+        <v>4.21</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>15.88</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42144</v>
+        <v>42145</v>
       </c>
       <c r="H3" t="n">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="I3" t="n">
         <v>225.3376063709212</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K3" t="n">
-        <v>-7.8</v>
+        <v>-10.73</v>
       </c>
       <c r="L3" t="n">
         <v>11.71</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>14.45</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42165</v>
+        <v>42166</v>
       </c>
       <c r="H4" t="n">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="I4" t="n">
         <v>195.6858300233474</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K4" t="n">
-        <v>-12.78</v>
+        <v>-14.98</v>
       </c>
       <c r="L4" t="n">
-        <v>14.1</v>
+        <v>15.42</v>
       </c>
       <c r="M4" t="n">
         <v>0.92</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,25 +764,25 @@
         <v>14.92</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42178</v>
+        <v>42179</v>
       </c>
       <c r="H5" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="I5" t="n">
         <v>215.871283749489</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K5" t="n">
-        <v>-10.36</v>
+        <v>-11.92</v>
       </c>
       <c r="L5" t="n">
-        <v>13.47</v>
+        <v>14.51</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.41</v>
       </c>
       <c r="N5" t="n">
         <v>3.11</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>10.36</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H6" t="n">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="I6" t="n">
         <v>207.8712182128349</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.93</v>
+        <v>-9.26</v>
       </c>
       <c r="L6" t="n">
-        <v>6.02</v>
+        <v>12.5</v>
       </c>
       <c r="M6" t="n">
-        <v>3.57</v>
+        <v>3.74</v>
       </c>
       <c r="N6" t="n">
-        <v>4.15</v>
+        <v>8.41</v>
       </c>
       <c r="O6" t="n">
         <v>1.41</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>15.9</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42362</v>
+        <v>42366</v>
       </c>
       <c r="H7" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="I7" t="n">
         <v>174.5727189296115</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K7" t="n">
-        <v>12.24</v>
+        <v>10.2</v>
       </c>
       <c r="L7" t="n">
         <v>7.14</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>11.43</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42384</v>
+        <v>42387</v>
       </c>
       <c r="H8" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I8" t="n">
         <v>166.3352067031629</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.11</v>
+        <v>-7.39</v>
       </c>
       <c r="L8" t="n">
-        <v>5.68</v>
+        <v>11.36</v>
       </c>
       <c r="M8" t="n">
         <v>1.15</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>12.98</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42432</v>
+        <v>42433</v>
       </c>
       <c r="H9" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I9" t="n">
         <v>166.8849417126666</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.61</v>
+        <v>-3.07</v>
       </c>
       <c r="L9" t="n">
         <v>8.59</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>13.14</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42591</v>
+        <v>42592</v>
       </c>
       <c r="H10" t="n">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="I10" t="n">
         <v>195.2421696132712</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K10" t="n">
-        <v>19.05</v>
+        <v>16.07</v>
       </c>
       <c r="L10" t="n">
         <v>3.57</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>11.32</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42632</v>
+        <v>42633</v>
       </c>
       <c r="H11" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I11" t="n">
         <v>200.4245086438326</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.54</v>
+        <v>-3.59</v>
       </c>
       <c r="L11" t="n">
-        <v>4.62</v>
+        <v>6.67</v>
       </c>
       <c r="M11" t="n">
         <v>2.02</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>7.6</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42705</v>
+        <v>42706</v>
       </c>
       <c r="H12" t="n">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="I12" t="n">
         <v>240.8614822445604</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K12" t="n">
-        <v>20.3</v>
+        <v>18.32</v>
       </c>
       <c r="L12" t="n">
         <v>1.98</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>12.75</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42713</v>
+        <v>42716</v>
       </c>
       <c r="H13" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I13" t="n">
         <v>267.9738766482031</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>-11.3</v>
+        <v>-12.13</v>
       </c>
       <c r="L13" t="n">
         <v>18.41</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>12.72</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42748</v>
+        <v>42751</v>
       </c>
       <c r="H14" t="n">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="I14" t="n">
         <v>237.5801875202023</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K14" t="n">
-        <v>-10.45</v>
+        <v>-11.57</v>
       </c>
       <c r="L14" t="n">
-        <v>11.57</v>
+        <v>11.94</v>
       </c>
       <c r="M14" t="n">
         <v>1.2</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>10.46</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42816</v>
+        <v>42817</v>
       </c>
       <c r="H15" t="n">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="I15" t="n">
         <v>235.4338154720781</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K15" t="n">
-        <v>0.84</v>
+        <v>-2.95</v>
       </c>
       <c r="L15" t="n">
         <v>5.06</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>9.43</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42845</v>
+        <v>42846</v>
       </c>
       <c r="H16" t="n">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="I16" t="n">
         <v>226.4219265413622</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K16" t="n">
-        <v>-6.15</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>7.79</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M16" t="n">
         <v>0.82</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>11.84</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42895</v>
+        <v>42898</v>
       </c>
       <c r="H17" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="I17" t="n">
         <v>212.7652495549088</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K17" t="n">
-        <v>6.25</v>
+        <v>4.91</v>
       </c>
       <c r="L17" t="n">
         <v>11.61</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>9.130000000000001</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42956</v>
+        <v>42957</v>
       </c>
       <c r="H18" t="n">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="I18" t="n">
         <v>216.3728358185393</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K18" t="n">
-        <v>2.35</v>
+        <v>-1.41</v>
       </c>
       <c r="L18" t="n">
-        <v>1.88</v>
+        <v>4.69</v>
       </c>
       <c r="M18" t="n">
         <v>0.91</v>
       </c>
       <c r="N18" t="n">
-        <v>2.68</v>
+        <v>3.67</v>
       </c>
       <c r="O18" t="n">
         <v>1.43</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>9.6</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42984</v>
+        <v>42985</v>
       </c>
       <c r="H19" t="n">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I19" t="n">
         <v>218.8518706605034</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.81</v>
+        <v>-5.71</v>
       </c>
       <c r="L19" t="n">
-        <v>5.24</v>
+        <v>8.1</v>
       </c>
       <c r="M19" t="n">
         <v>1.02</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>8.119999999999999</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43004</v>
+        <v>43005</v>
       </c>
       <c r="H20" t="n">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="I20" t="n">
         <v>208.2291576165162</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.5</v>
+        <v>-7.66</v>
       </c>
       <c r="L20" t="n">
-        <v>6.76</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="M20" t="n">
         <v>0.47</v>
       </c>
       <c r="N20" t="n">
-        <v>2.76</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
         <v>1.83</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>10.91</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43019</v>
+        <v>43020</v>
       </c>
       <c r="H21" t="n">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="I21" t="n">
         <v>221.7713579268777</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K21" t="n">
-        <v>-7.8</v>
+        <v>-10.24</v>
       </c>
       <c r="L21" t="n">
-        <v>10.24</v>
+        <v>11.22</v>
       </c>
       <c r="M21" t="n">
         <v>2.4</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>9.359999999999999</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43040</v>
+        <v>43041</v>
       </c>
       <c r="H22" t="n">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="I22" t="n">
         <v>207.192996522327</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.52</v>
+        <v>-9.73</v>
       </c>
       <c r="L22" t="n">
-        <v>8.85</v>
+        <v>10.18</v>
       </c>
       <c r="M22" t="n">
         <v>1.8</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>10.59</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43173</v>
+        <v>43174</v>
       </c>
       <c r="H23" t="n">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="I23" t="n">
         <v>156.0147056260108</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K23" t="n">
-        <v>25.49</v>
+        <v>19.12</v>
       </c>
       <c r="L23" t="n">
         <v>2.94</v>
@@ -1752,7 +2027,7 @@
         <v>2.6</v>
       </c>
       <c r="N23" t="n">
-        <v>4.97</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O23" t="n">
         <v>-2.39</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1788,25 +2075,25 @@
         <v>13.05</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43181</v>
+        <v>43182</v>
       </c>
       <c r="H24" t="n">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="I24" t="n">
         <v>147.5648198111055</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K24" t="n">
-        <v>-9.699999999999999</v>
+        <v>-14.55</v>
       </c>
       <c r="L24" t="n">
-        <v>11.52</v>
+        <v>15.15</v>
       </c>
       <c r="M24" t="n">
-        <v>0.65</v>
+        <v>2.01</v>
       </c>
       <c r="N24" t="n">
         <v>5.56</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>15.48</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43203</v>
+        <v>43206</v>
       </c>
       <c r="H25" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I25" t="n">
         <v>152.8360050267607</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K25" t="n">
-        <v>-7.8</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>9.93</v>
+        <v>10.64</v>
       </c>
       <c r="M25" t="n">
         <v>2.26</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>11.47</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43277</v>
+        <v>43278</v>
       </c>
       <c r="H26" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I26" t="n">
         <v>149.8306081668981</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.95</v>
+        <v>-3.9</v>
       </c>
       <c r="L26" t="n">
         <v>7.79</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,25 +2282,25 @@
         <v>11.2</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43291</v>
+        <v>43292</v>
       </c>
       <c r="H27" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="I27" t="n">
         <v>158.4639552519567</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.05</v>
+        <v>-7.43</v>
       </c>
       <c r="L27" t="n">
-        <v>4.73</v>
+        <v>10.14</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="N27" t="n">
         <v>4.17</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>10.11</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43346</v>
+        <v>43347</v>
       </c>
       <c r="H28" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="I28" t="n">
         <v>160.9363145936458</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K28" t="n">
-        <v>3.77</v>
+        <v>-2.52</v>
       </c>
       <c r="L28" t="n">
         <v>6.29</v>
@@ -2037,7 +2372,7 @@
         <v>3.12</v>
       </c>
       <c r="N28" t="n">
-        <v>3.75</v>
+        <v>6.06</v>
       </c>
       <c r="O28" t="n">
         <v>3.25</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>14.01</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43388</v>
+        <v>43389</v>
       </c>
       <c r="H29" t="n">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="I29" t="n">
         <v>159.1341525059918</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K29" t="n">
-        <v>5.81</v>
+        <v>-3.23</v>
       </c>
       <c r="L29" t="n">
         <v>7.1</v>
@@ -2094,7 +2441,7 @@
         <v>3.18</v>
       </c>
       <c r="N29" t="n">
-        <v>7.19</v>
+        <v>9.59</v>
       </c>
       <c r="O29" t="n">
         <v>-6.06</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>20.57</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43489</v>
+        <v>43490</v>
       </c>
       <c r="H30" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I30" t="n">
         <v>142.8835895638443</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K30" t="n">
-        <v>-10</v>
+        <v>-11.25</v>
       </c>
       <c r="L30" t="n">
         <v>15</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43525</v>
+        <v>43529</v>
       </c>
       <c r="H31" t="n">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="I31" t="n">
         <v>142.7569987658106</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K31" t="n">
-        <v>4.93</v>
+        <v>-2.82</v>
       </c>
       <c r="L31" t="n">
-        <v>2.11</v>
+        <v>3.52</v>
       </c>
       <c r="M31" t="n">
         <v>1.49</v>
       </c>
       <c r="N31" t="n">
-        <v>3.05</v>
+        <v>8.15</v>
       </c>
       <c r="O31" t="n">
         <v>-1.39</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>13.25</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43675</v>
+        <v>43676</v>
       </c>
       <c r="H32" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I32" t="n">
         <v>161.4024843618721</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K32" t="n">
-        <v>10.96</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="L32" t="n">
         <v>7.53</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>6</v>
+      </c>
+      <c r="U32" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>14.16</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43703</v>
+        <v>43704</v>
       </c>
       <c r="H33" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="I33" t="n">
         <v>179.4623949271297</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K33" t="n">
-        <v>-12.66</v>
+        <v>-15.82</v>
       </c>
       <c r="L33" t="n">
-        <v>13.92</v>
+        <v>16.46</v>
       </c>
       <c r="M33" t="n">
         <v>1.83</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>11.12</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43859</v>
+        <v>43860</v>
       </c>
       <c r="H34" t="n">
-        <v>276</v>
+        <v>255</v>
       </c>
       <c r="I34" t="n">
         <v>255.6284237698575</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K34" t="n">
-        <v>50.82</v>
+        <v>39.34</v>
       </c>
       <c r="L34" t="n">
         <v>8.74</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>6</v>
+      </c>
+      <c r="U34" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>15.5</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43977</v>
+        <v>43978</v>
       </c>
       <c r="H35" t="n">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="I35" t="n">
         <v>248.3615644953381</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K35" t="n">
-        <v>5.88</v>
+        <v>-0.78</v>
       </c>
       <c r="L35" t="n">
         <v>9.800000000000001</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>15.7</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44154</v>
+        <v>44155</v>
       </c>
       <c r="H36" t="n">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I36" t="n">
         <v>323.9908010141045</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K36" t="n">
-        <v>26.07</v>
+        <v>25.29</v>
       </c>
       <c r="L36" t="n">
         <v>8.949999999999999</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>7</v>
+      </c>
+      <c r="U36" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>9.58</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44176</v>
+        <v>44179</v>
       </c>
       <c r="H37" t="n">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="I37" t="n">
         <v>339.8008186202239</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.73</v>
+        <v>-5.59</v>
       </c>
       <c r="L37" t="n">
         <v>6.52</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>9.529999999999999</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44225</v>
+        <v>44228</v>
       </c>
       <c r="H38" t="n">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="I38" t="n">
         <v>325.8384554464649</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K38" t="n">
-        <v>-3.24</v>
+        <v>-5.88</v>
       </c>
       <c r="L38" t="n">
-        <v>4.71</v>
+        <v>6.47</v>
       </c>
       <c r="M38" t="n">
         <v>0.3</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>10.76</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44333</v>
+        <v>44334</v>
       </c>
       <c r="H39" t="n">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="I39" t="n">
         <v>319.7893110480139</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K39" t="n">
-        <v>2.81</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L39" t="n">
         <v>4.06</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>11.65</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44363</v>
+        <v>44364</v>
       </c>
       <c r="H40" t="n">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="I40" t="n">
         <v>298.3803085623748</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.64</v>
+        <v>-7.74</v>
       </c>
       <c r="L40" t="n">
-        <v>6.19</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M40" t="n">
         <v>4.92</v>
       </c>
       <c r="N40" t="n">
-        <v>3.09</v>
+        <v>3.25</v>
       </c>
       <c r="O40" t="n">
         <v>3.86</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>9.359999999999999</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44389</v>
+        <v>44390</v>
       </c>
       <c r="H41" t="n">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="I41" t="n">
         <v>319.8312230130473</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K41" t="n">
-        <v>0.34</v>
+        <v>-7.38</v>
       </c>
       <c r="L41" t="n">
-        <v>5.7</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="M41" t="n">
         <v>1.34</v>
       </c>
       <c r="N41" t="n">
-        <v>1.68</v>
+        <v>7.74</v>
       </c>
       <c r="O41" t="n">
         <v>-3.25</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>11.28</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44417</v>
+        <v>44418</v>
       </c>
       <c r="H42" t="n">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="I42" t="n">
         <v>312.4632361230257</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.88</v>
+        <v>-4.38</v>
       </c>
       <c r="L42" t="n">
         <v>7.19</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>14.38</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44442</v>
+        <v>44445</v>
       </c>
       <c r="H43" t="n">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="I43" t="n">
         <v>322.5166579403435</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K43" t="n">
-        <v>-4.25</v>
+        <v>-7.52</v>
       </c>
       <c r="L43" t="n">
-        <v>6.21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M43" t="n">
         <v>0.99</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>10.94</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44490</v>
+        <v>44491</v>
       </c>
       <c r="H44" t="n">
-        <v>376</v>
+        <v>359</v>
       </c>
       <c r="I44" t="n">
         <v>360.9129576706968</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K44" t="n">
-        <v>14.29</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="L44" t="n">
         <v>4.26</v>
@@ -2949,7 +3476,7 @@
         <v>2.42</v>
       </c>
       <c r="N44" t="n">
-        <v>4.35</v>
+        <v>4.52</v>
       </c>
       <c r="O44" t="n">
         <v>3.13</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>20.19</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44512</v>
+        <v>44515</v>
       </c>
       <c r="H45" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="I45" t="n">
         <v>391.4996448843041</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K45" t="n">
-        <v>-8.640000000000001</v>
+        <v>-9.75</v>
       </c>
       <c r="L45" t="n">
-        <v>10.31</v>
+        <v>11.98</v>
       </c>
       <c r="M45" t="n">
         <v>1.17</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>10.73</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44518</v>
+        <v>44522</v>
       </c>
       <c r="H46" t="n">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="I46" t="n">
         <v>351.7211922818369</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K46" t="n">
-        <v>-8.119999999999999</v>
+        <v>-12.44</v>
       </c>
       <c r="L46" t="n">
-        <v>9.140000000000001</v>
+        <v>12.69</v>
       </c>
       <c r="M46" t="n">
         <v>0.26</v>
       </c>
       <c r="N46" t="n">
-        <v>3.36</v>
+        <v>4.7</v>
       </c>
       <c r="O46" t="n">
         <v>1.03</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>16.84</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44630</v>
+        <v>44631</v>
       </c>
       <c r="H47" t="n">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="I47" t="n">
         <v>277.2455895568215</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K47" t="n">
-        <v>22.9</v>
+        <v>19.42</v>
       </c>
       <c r="L47" t="n">
         <v>6.38</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>17.04</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44669</v>
+        <v>44670</v>
       </c>
       <c r="H48" t="n">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="I48" t="n">
         <v>270.6056829338496</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.72</v>
+        <v>-3.6</v>
       </c>
       <c r="L48" t="n">
         <v>5.4</v>
@@ -3177,7 +3752,7 @@
         <v>0.38</v>
       </c>
       <c r="N48" t="n">
-        <v>2.49</v>
+        <v>2.9</v>
       </c>
       <c r="O48" t="n">
         <v>4.51</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>11.27</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44711</v>
+        <v>44712</v>
       </c>
       <c r="H49" t="n">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="I49" t="n">
         <v>264.5580189405086</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K49" t="n">
-        <v>3.36</v>
+        <v>-2.24</v>
       </c>
       <c r="L49" t="n">
         <v>7.84</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>14.05</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44729</v>
+        <v>44732</v>
       </c>
       <c r="H50" t="n">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="I50" t="n">
         <v>241.1199634747441</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K50" t="n">
-        <v>-10.95</v>
+        <v>-14.6</v>
       </c>
       <c r="L50" t="n">
-        <v>11.68</v>
+        <v>15.69</v>
       </c>
       <c r="M50" t="n">
         <v>1.16</v>
       </c>
       <c r="N50" t="n">
-        <v>3.86</v>
+        <v>4.1</v>
       </c>
       <c r="O50" t="n">
         <v>5.79</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>14.46</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44756</v>
+        <v>44757</v>
       </c>
       <c r="H51" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I51" t="n">
         <v>267.8470660835615</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K51" t="n">
-        <v>-14.1</v>
+        <v>-14.96</v>
       </c>
       <c r="L51" t="n">
         <v>15.81</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44774</v>
+        <v>44775</v>
       </c>
       <c r="H52" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I52" t="n">
         <v>264.4492682956516</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.49</v>
+        <v>-1.86</v>
       </c>
       <c r="L52" t="n">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="M52" t="n">
         <v>0.36</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>7.6</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44838</v>
+        <v>44840</v>
       </c>
       <c r="H53" t="n">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="I53" t="n">
         <v>260.7430823418166</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K53" t="n">
-        <v>3.41</v>
+        <v>0.38</v>
       </c>
       <c r="L53" t="n">
         <v>3.79</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>10.43</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H54" t="n">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="I54" t="n">
         <v>311.4677598332647</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K54" t="n">
-        <v>20.15</v>
+        <v>17.49</v>
       </c>
       <c r="L54" t="n">
         <v>3.04</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>8.52</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44938</v>
+        <v>44939</v>
       </c>
       <c r="H55" t="n">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="I55" t="n">
         <v>314.7431661211962</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K55" t="n">
-        <v>2.27</v>
+        <v>-3.88</v>
       </c>
       <c r="L55" t="n">
-        <v>2.91</v>
+        <v>4.21</v>
       </c>
       <c r="M55" t="n">
         <v>0.68</v>
       </c>
       <c r="N55" t="n">
-        <v>2.03</v>
+        <v>6.29</v>
       </c>
       <c r="O55" t="n">
         <v>-2.22</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>11.2</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44958</v>
+        <v>44959</v>
       </c>
       <c r="H56" t="n">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="I56" t="n">
         <v>296.7945537980468</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K56" t="n">
-        <v>-7.17</v>
+        <v>-8.41</v>
       </c>
       <c r="L56" t="n">
-        <v>7.79</v>
+        <v>9.35</v>
       </c>
       <c r="M56" t="n">
         <v>1.25</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>10.94</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44999</v>
+        <v>45000</v>
       </c>
       <c r="H57" t="n">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="I57" t="n">
         <v>298.7433905571411</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.34</v>
+        <v>-1.7</v>
       </c>
       <c r="L57" t="n">
         <v>4.08</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>7.28</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45041</v>
+        <v>45042</v>
       </c>
       <c r="H58" t="n">
-        <v>298</v>
+        <v>279</v>
       </c>
       <c r="I58" t="n">
         <v>284.6780880931791</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.33</v>
+        <v>-6.69</v>
       </c>
       <c r="L58" t="n">
-        <v>4.01</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="M58" t="n">
-        <v>-0</v>
+        <v>0.67</v>
       </c>
       <c r="N58" t="n">
-        <v>3.3</v>
+        <v>6.38</v>
       </c>
       <c r="O58" t="n">
         <v>1.36</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>11.1</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45075</v>
+        <v>45076</v>
       </c>
       <c r="H59" t="n">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="I59" t="n">
         <v>285.0717736055691</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K59" t="n">
-        <v>0.36</v>
+        <v>-3.58</v>
       </c>
       <c r="L59" t="n">
         <v>6.09</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>10.37</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45335</v>
+        <v>45336</v>
       </c>
       <c r="H60" t="n">
-        <v>684</v>
+        <v>672</v>
       </c>
       <c r="I60" t="n">
         <v>680.7395102089563</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K60" t="n">
-        <v>136.68</v>
+        <v>132.53</v>
       </c>
       <c r="L60" t="n">
         <v>3.46</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>178</v>
+        <v>179</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>9</v>
+      </c>
+      <c r="U60" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>15.56</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45390</v>
+        <v>45391</v>
       </c>
       <c r="H61" t="n">
-        <v>719</v>
+        <v>746</v>
       </c>
       <c r="I61" t="n">
         <v>719.6208984817318</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K61" t="n">
-        <v>-6.99</v>
+        <v>-11.01</v>
       </c>
       <c r="L61" t="n">
         <v>15.48</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>11.06</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45441</v>
+        <v>45442</v>
       </c>
       <c r="H62" t="n">
-        <v>750</v>
+        <v>721</v>
       </c>
       <c r="I62" t="n">
         <v>735.4849011854301</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K62" t="n">
-        <v>0.54</v>
+        <v>-3.35</v>
       </c>
       <c r="L62" t="n">
         <v>4.16</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>12.81</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45455</v>
+        <v>45456</v>
       </c>
       <c r="H63" t="n">
-        <v>759</v>
+        <v>776</v>
       </c>
       <c r="I63" t="n">
         <v>772.636609508529</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K63" t="n">
-        <v>-5.27</v>
+        <v>-7.63</v>
       </c>
       <c r="L63" t="n">
-        <v>6.66</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="M63" t="n">
         <v>4.96</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>13.9</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45610</v>
+        <v>45614</v>
       </c>
       <c r="H64" t="n">
-        <v>1190</v>
+        <v>1182</v>
       </c>
       <c r="I64" t="n">
         <v>1189.46292334229</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="K64" t="n">
-        <v>53.35</v>
+        <v>52.32</v>
       </c>
       <c r="L64" t="n">
         <v>6.7</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>6</v>
+      </c>
+      <c r="U64" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>12.63</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45631</v>
+        <v>45632</v>
       </c>
       <c r="H65" t="n">
-        <v>1298</v>
+        <v>1384</v>
       </c>
       <c r="I65" t="n">
         <v>1331.270181169281</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K65" t="n">
-        <v>-9.81</v>
+        <v>-17.09</v>
       </c>
       <c r="L65" t="n">
-        <v>10.32</v>
+        <v>19.29</v>
       </c>
       <c r="M65" t="n">
         <v>0.97</v>
       </c>
       <c r="N65" t="n">
-        <v>3.3</v>
+        <v>6.63</v>
       </c>
       <c r="O65" t="n">
         <v>-0.67</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>13.23</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45659</v>
+        <v>45660</v>
       </c>
       <c r="H66" t="n">
-        <v>1268</v>
+        <v>1232</v>
       </c>
       <c r="I66" t="n">
         <v>1238.098266871095</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K66" t="n">
-        <v>-8.380000000000001</v>
+        <v>-10.98</v>
       </c>
       <c r="L66" t="n">
-        <v>10.69</v>
+        <v>11.27</v>
       </c>
       <c r="M66" t="n">
         <v>1.87</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>10.98</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45735</v>
+        <v>45736</v>
       </c>
       <c r="H67" t="n">
-        <v>1042</v>
+        <v>1077</v>
       </c>
       <c r="I67" t="n">
         <v>1052.966144290344</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K67" t="n">
-        <v>15.42</v>
+        <v>12.58</v>
       </c>
       <c r="L67" t="n">
         <v>4.14</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>13.79</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45848</v>
+        <v>45849</v>
       </c>
       <c r="H68" t="n">
-        <v>1666</v>
+        <v>1610</v>
       </c>
       <c r="I68" t="n">
         <v>1640.082349895376</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K68" t="n">
-        <v>54.69</v>
+        <v>49.49</v>
       </c>
       <c r="L68" t="n">
         <v>15.78</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>5</v>
+      </c>
+      <c r="U68" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>11.35</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45881</v>
+        <v>45882</v>
       </c>
       <c r="H69" t="n">
-        <v>1630</v>
+        <v>1668</v>
       </c>
       <c r="I69" t="n">
         <v>1654.541398403305</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.24</v>
+        <v>-3.6</v>
       </c>
       <c r="L69" t="n">
         <v>4.91</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>9.529999999999999</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45895</v>
+        <v>45897</v>
       </c>
       <c r="H70" t="n">
-        <v>1538</v>
+        <v>1480</v>
       </c>
       <c r="I70" t="n">
         <v>1515.551948623313</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K70" t="n">
-        <v>-7.79</v>
+        <v>-11.27</v>
       </c>
       <c r="L70" t="n">
-        <v>8.029999999999999</v>
+        <v>11.45</v>
       </c>
       <c r="M70" t="n">
         <v>0.06</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>12.03</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45931</v>
+        <v>45933</v>
       </c>
       <c r="H71" t="n">
-        <v>1600</v>
+        <v>1629</v>
       </c>
       <c r="I71" t="n">
         <v>1619.785943606059</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K71" t="n">
-        <v>-8.109999999999999</v>
+        <v>-10.07</v>
       </c>
       <c r="L71" t="n">
-        <v>9.800000000000001</v>
+        <v>11.01</v>
       </c>
       <c r="M71" t="n">
         <v>1.01</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>8.41</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46052</v>
+        <v>46054</v>
       </c>
       <c r="H72" t="n">
-        <v>2528</v>
+        <v>2233.3</v>
       </c>
       <c r="I72" t="n">
         <v>2342.768150074908</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="K72" t="n">
-        <v>55.19</v>
+        <v>37.1</v>
       </c>
       <c r="L72" t="n">
         <v>2.03</v>
       </c>
       <c r="M72" t="n">
-        <v>2.22</v>
+        <v>9.02</v>
       </c>
       <c r="N72" t="n">
-        <v>5.88</v>
+        <v>11.66</v>
       </c>
       <c r="O72" t="n">
         <v>1.81</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>5</v>
+      </c>
+      <c r="U72" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>18.53</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="H73" t="n">
-        <v>2555.6</v>
+        <v>2671.8</v>
       </c>
       <c r="I73" t="n">
         <v>2647.192798439325</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K73" t="n">
-        <v>-14.43</v>
+        <v>-19.63</v>
       </c>
       <c r="L73" t="n">
-        <v>17.49</v>
+        <v>20.05</v>
       </c>
       <c r="M73" t="n">
         <v>7.68</v>
@@ -4611,7 +5486,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>12.61</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="H74" t="n">
-        <v>2414.5</v>
+        <v>2314.4</v>
       </c>
       <c r="I74" t="n">
         <v>2338.957120874828</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K74" t="n">
-        <v>-9.630000000000001</v>
+        <v>-13.38</v>
       </c>
       <c r="L74" t="n">
-        <v>10.29</v>
+        <v>15.41</v>
       </c>
       <c r="M74" t="n">
         <v>1.79</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>15.16</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="H75" t="n">
-        <v>2657.5</v>
+        <v>2669.4</v>
       </c>
       <c r="I75" t="n">
         <v>2665.297358882251</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K75" t="n">
-        <v>-14.82</v>
+        <v>-15.34</v>
       </c>
       <c r="L75" t="n">
-        <v>15.87</v>
+        <v>17.04</v>
       </c>
       <c r="M75" t="n">
         <v>4.28</v>
@@ -4725,7 +5624,19 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>11.98</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="H76" t="n">
-        <v>3158.5</v>
+        <v>2954.5</v>
       </c>
       <c r="I76" t="n">
         <v>3096.288235742582</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K76" t="n">
-        <v>18.32</v>
+        <v>10.68</v>
       </c>
       <c r="L76" t="n">
         <v>1.74</v>
@@ -4773,7 +5684,7 @@
         <v>1.26</v>
       </c>
       <c r="N76" t="n">
-        <v>4.5</v>
+        <v>6.46</v>
       </c>
       <c r="O76" t="n">
         <v>0.45</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>3</v>
+      </c>
+      <c r="U76" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>15.86</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="H77" t="n">
-        <v>2759.3</v>
+        <v>2895</v>
       </c>
       <c r="I77" t="n">
         <v>2859.229965062444</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K77" t="n">
-        <v>6.61</v>
+        <v>2.01</v>
       </c>
       <c r="L77" t="n">
         <v>7.53</v>
@@ -4830,7 +5753,7 @@
         <v>1.96</v>
       </c>
       <c r="N77" t="n">
-        <v>4.6</v>
+        <v>4.92</v>
       </c>
       <c r="O77" t="n">
         <v>-6.46</v>
@@ -4839,7 +5762,19 @@
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>3</v>
+      </c>
+      <c r="U77" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>12.38</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="H78" t="n">
-        <v>3113.7</v>
+        <v>3020.3</v>
       </c>
       <c r="I78" t="n">
         <v>3080.01278388043</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K78" t="n">
-        <v>7.55</v>
+        <v>4.33</v>
       </c>
       <c r="L78" t="n">
         <v>5.26</v>
@@ -4896,7 +5831,19 @@
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>3</v>
+      </c>
+      <c r="U78" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -4947,6 +5894,14 @@
       <c r="Q79" t="n">
         <v>4</v>
       </c>
+      <c r="R79" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9905,7 +10860,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54.3</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="6">
@@ -9915,7 +10870,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -9925,7 +10880,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8">
@@ -9935,7 +10890,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -9945,7 +10900,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10">
@@ -9955,7 +10910,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>120.2</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11">
@@ -9995,7 +10950,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.49</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="15">
@@ -10005,7 +10960,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.91</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -10015,7 +10970,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.07</v>
+        <v>-4.55</v>
       </c>
     </row>
     <row r="17">
@@ -10025,7 +10980,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>136.68</v>
+        <v>132.53</v>
       </c>
     </row>
     <row r="18">
@@ -10035,7 +10990,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>42.9</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="19">
@@ -10045,7 +11000,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.64</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="20">
@@ -10055,7 +11010,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.76</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="21">
@@ -10065,7 +11020,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18.41</v>
+        <v>20.05</v>
       </c>
     </row>
     <row r="22">
@@ -10075,7 +11030,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23">
@@ -10085,7 +11040,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24">
@@ -10095,7 +11050,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="25">
@@ -10115,7 +11070,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.84</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="27">
@@ -10135,7 +11090,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29">
